--- a/data/trans_dic/IP13_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas</t>
+          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 12,11</t>
+          <t>1,24; 11,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 20,67</t>
+          <t>5,89; 21,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 13,95</t>
+          <t>4,15; 13,48</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,54</t>
+          <t>2,63; 5,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,94</t>
+          <t>2,4; 5,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,8</t>
+          <t>2,78; 4,74</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,99</t>
+          <t>1,97; 7,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,93</t>
+          <t>3,35; 10,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,99</t>
+          <t>3,37; 7,69</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,47</t>
+          <t>2,88; 5,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,2</t>
+          <t>3,45; 6,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,55</t>
+          <t>3,58; 5,44</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7098</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9823</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>676; 6178</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3653; 13235</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4839; 15732</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>17843</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18591</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36433</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>12071; 26000</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12415; 27480</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>27166; 46293</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6290</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10864</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17154</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2943; 11540</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6118; 18654</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11181; 25532</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>26858</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36553</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>63411</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>19110; 37128</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26271; 47471</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>51064; 77459</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP13_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,3</t>
+          <t>1,22; 12,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 21,35</t>
+          <t>5,92; 20,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 13,48</t>
+          <t>4,56; 13,75</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,66</t>
+          <t>2,41; 5,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,32</t>
+          <t>2,36; 5,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,74</t>
+          <t>2,81; 4,88</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,72</t>
+          <t>2,12; 8,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,21</t>
+          <t>3,35; 9,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,69</t>
+          <t>3,45; 8,0</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,59</t>
+          <t>2,91; 5,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,24</t>
+          <t>3,61; 6,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,44</t>
+          <t>3,58; 5,43</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>676; 6178</t>
+          <t>668; 6615</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3653; 13235</t>
+          <t>3670; 12838</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4839; 15732</t>
+          <t>5318; 16042</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12071; 26000</t>
+          <t>11101; 25316</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12415; 27480</t>
+          <t>12183; 26639</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27166; 46293</t>
+          <t>27428; 47600</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2943; 11540</t>
+          <t>3172; 12425</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6118; 18654</t>
+          <t>6113; 18089</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11181; 25532</t>
+          <t>11444; 26583</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19110; 37128</t>
+          <t>19317; 36312</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26271; 47471</t>
+          <t>27485; 48516</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51064; 77459</t>
+          <t>51064; 77434</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 12,1</t>
+          <t>6,22; 21,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 20,7</t>
+          <t>1,47; 13,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 13,75</t>
+          <t>5,16; 15,51</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,51</t>
+          <t>2,33; 4,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,16</t>
+          <t>2,76; 5,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,88</t>
+          <t>2,81; 4,81</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 8,31</t>
+          <t>3,62; 10,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,91</t>
+          <t>1,97; 8,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,0</t>
+          <t>3,48; 8,1</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,47</t>
+          <t>3,71; 6,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,37</t>
+          <t>3,0; 5,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,43</t>
+          <t>3,7; 5,71</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>9494</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>668; 6615</t>
+          <t>3530; 12339</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3670; 12838</t>
+          <t>689; 6393</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5318; 16042</t>
+          <t>5337; 16052</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>34041</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11101; 25316</t>
+          <t>11070; 23491</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12183; 26639</t>
+          <t>11896; 24717</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27428; 47600</t>
+          <t>25483; 43679</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17154</t>
+          <t>16939</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3172; 12425</t>
+          <t>6073; 17522</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6113; 18089</t>
+          <t>2949; 12351</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11444; 26583</t>
+          <t>11077; 25741</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26858</t>
+          <t>34234</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>60473</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19317; 36312</t>
+          <t>26014; 44933</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27485; 48516</t>
+          <t>18837; 35066</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51064; 77434</t>
+          <t>49216; 75809</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6,22; 21,75</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 13,67</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5,16; 15,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2,33; 4,94</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2,76; 5,73</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2,81; 4,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3,62; 10,44</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,97; 8,24</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3,48; 8,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>3,71; 6,42</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3,0; 5,58</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3,7; 5,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1216545488407493</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.05544136169190904</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.0917388556012316</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6902</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2592</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9494</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.06222263597080721</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.01473493530908065</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.05156991338933515</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3530; 12339</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>689; 6393</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5337; 16052</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.217496380728584</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1367308638589565</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1551027884740994</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.03550322321505892</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.03974184522436739</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.03751957627526589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>16888</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>17153</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>34041</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.02327168935916723</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.02756256905319629</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.02808733034694502</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>11070; 23491</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>11896; 24717</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>25483; 43679</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.04938371555130069</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.05726885058824439</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.04814332681693638</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.06221365953848398</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.04330023390441333</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.05328966520720343</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>10445</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6494</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16939</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.03617133092073333</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.0196630238795647</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.03484798392029936</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>6073; 17522</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2949; 12351</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11077; 25741</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1043695841229482</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.08235507746608291</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.08098121758107382</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.04888587545735911</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.04175947320814137</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.04551565265798582</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>34234</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>26239</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>60473</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.03714727948428735</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.02997839721859843</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.03704296957760686</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>26014; 44933</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>18837; 35066</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>49216; 75809</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.06416299531432031</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.05580718646779607</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.05705805634027417</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>6902</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2592</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>9494</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>3530</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>689</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>5337</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>12339</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>6393</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>16052</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>16888</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>17153</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>34041</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>11070</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>11896</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>25483</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>23491</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>24717</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>43679</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>10445</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>6494</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>16939</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>6073</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2949</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>11077</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>17522</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>12351</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>25741</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>34234</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>26239</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>60473</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>26014</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>18837</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>49216</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>44933</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>35066</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>75809</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>